--- a/output/pdf_financials_xlsx/BRC.xlsx
+++ b/output/pdf_financials_xlsx/BRC.xlsx
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.355907</v>
+        <v>-0.355907</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.600857</v>
+        <v>-0.600857</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.355907</v>
+        <v>-0.355907</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.600857</v>
+        <v>-0.600857</v>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.355907</v>
+        <v>-0.355907</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.600857</v>
+        <v>-0.600857</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-5.084386</v>
+        <v>5.084386</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-7.510712</v>
+        <v>7.510712</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.355907</v>
+        <v>-0.355907</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.600857</v>
+        <v>-0.600857</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.356224</v>
+        <v>-0.35559</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.601028</v>
+        <v>-0.6006860000000001</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -6371,46 +6371,46 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.171133</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.171133</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.171133</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.171133</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.171133</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.171133</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.264769</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.565505</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.085554</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>9.315759999999999</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>9.514436999999999</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.233351</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>10.242291</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>10.822381</v>
       </c>
     </row>
     <row r="93">
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.177747</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.157888</v>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
@@ -11360,7 +11360,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -13852,7 +13856,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -15980,7 +15988,11 @@
           <t>Reserves 171,133</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -17640,7 +17652,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -20938,7 +20954,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -23096,10 +23116,10 @@
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>0.355907</v>
+        <v>-0.355907</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>0.600857</v>
+        <v>-0.600857</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BRC.xlsx
+++ b/output/pdf_financials_xlsx/BRC.xlsx
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000122</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.11559</v>
+        <v>-0.115712</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.0564</v>
+        <v>-0.056406</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.114634</v>
+        <v>-0.114756</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.055699</v>
+        <v>-0.055705</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2920,28 +2920,28 @@
         <v>0.007651</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.015812</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003341</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.04788</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.09181400000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.210029</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.878066</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>8.535437999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.649175</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.656181</v>
@@ -3038,28 +3038,28 @@
         <v>0.007651</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.015812</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003341</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.04788</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.09181400000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.210029</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.878066</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>8.535437999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.649175</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.656181</v>
@@ -3746,28 +3746,28 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.015812</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.003341</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.315051</v>
+        <v>0.267171</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.17708</v>
+        <v>0.08526599999999999</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.381455</v>
+        <v>0.171426</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.0681</v>
+        <v>0.190034</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>8.674731</v>
+        <v>0.139293</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.894328</v>
+        <v>0.245153</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.40989</v>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -23756,7 +23756,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -24622,7 +24622,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
